--- a/dq_flux8turn.xlsx
+++ b/dq_flux8turn.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Lambda_d_matrix" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -834,66 +834,66 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lambda_d_matrix!$M$2:$M$20</c:f>
+              <c:f>Lambda_d_matrix!$L$2:$L$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>92.644999999999996</c:v>
+                  <c:v>119.24</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73.66</c:v>
+                  <c:v>109.31</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.63</c:v>
+                  <c:v>98.87</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>35.89</c:v>
+                  <c:v>88.01</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17.649999999999999</c:v>
+                  <c:v>77.209999999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>66.66</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-17.13</c:v>
+                  <c:v>56.42</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-33.93</c:v>
+                  <c:v>46.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-50.44</c:v>
+                  <c:v>36.93</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-66.974999999999994</c:v>
+                  <c:v>27.67</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-82.864999999999995</c:v>
+                  <c:v>18.73</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-96.385000000000005</c:v>
+                  <c:v>9.6199999999999992</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-109.255</c:v>
+                  <c:v>0.35</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-122.645</c:v>
+                  <c:v>-7.87</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-135.09</c:v>
+                  <c:v>-14.89</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-146.1</c:v>
+                  <c:v>-20.57</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-154.5</c:v>
+                  <c:v>-24.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-160.47999999999999</c:v>
+                  <c:v>-26.85</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-163.02500000000001</c:v>
+                  <c:v>-27.64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1003,11 +1003,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-204385376"/>
-        <c:axId val="-204387552"/>
+        <c:axId val="-753118400"/>
+        <c:axId val="-753119488"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-204385376"/>
+        <c:axId val="-753118400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1050,7 +1050,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-204387552"/>
+        <c:crossAx val="-753119488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1058,7 +1058,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-204387552"/>
+        <c:axId val="-753119488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1109,7 +1109,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-204385376"/>
+        <c:crossAx val="-753118400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1482,11 +1482,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-204384288"/>
-        <c:axId val="-204387008"/>
+        <c:axId val="-753128192"/>
+        <c:axId val="-753124928"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-204384288"/>
+        <c:axId val="-753128192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1529,7 +1529,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-204387008"/>
+        <c:crossAx val="-753124928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1537,7 +1537,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-204387008"/>
+        <c:axId val="-753124928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1588,7 +1588,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-204384288"/>
+        <c:crossAx val="-753128192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3191,41 +3191,41 @@
         <v>90</v>
       </c>
       <c r="B2">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C2">
-        <v>243.72</v>
+        <v>134.97999999999999</v>
       </c>
       <c r="D2">
-        <v>238.82</v>
+        <v>134.91999999999999</v>
       </c>
       <c r="E2">
-        <v>230.42</v>
+        <v>134.07</v>
       </c>
       <c r="F2">
-        <v>224.1</v>
+        <v>131.86000000000001</v>
       </c>
       <c r="G2">
-        <v>217.26</v>
+        <v>129.13</v>
       </c>
       <c r="H2">
-        <v>210.16</v>
+        <v>126.67</v>
       </c>
       <c r="I2">
-        <v>202.97</v>
+        <v>124.72</v>
       </c>
       <c r="J2">
-        <v>196.21</v>
+        <v>122.89</v>
       </c>
       <c r="K2">
-        <v>190.36</v>
+        <v>121.07</v>
       </c>
       <c r="L2">
-        <v>185.29</v>
+        <v>119.24</v>
       </c>
       <c r="M2">
         <f>L2/2</f>
-        <v>92.644999999999996</v>
+        <v>59.62</v>
       </c>
       <c r="N2">
         <v>90</v>
@@ -3273,41 +3273,41 @@
         <v>95</v>
       </c>
       <c r="B3">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C3">
-        <v>237.69</v>
+        <v>133.46</v>
       </c>
       <c r="D3">
-        <v>228.52</v>
+        <v>131.96</v>
       </c>
       <c r="E3">
-        <v>216.75</v>
+        <v>130.04</v>
       </c>
       <c r="F3">
-        <v>207.01</v>
+        <v>126.9</v>
       </c>
       <c r="G3">
-        <v>196.49</v>
+        <v>123.31</v>
       </c>
       <c r="H3">
-        <v>185.37</v>
+        <v>120.13</v>
       </c>
       <c r="I3">
-        <v>174.24</v>
+        <v>117.4</v>
       </c>
       <c r="J3">
-        <v>164.22</v>
+        <v>114.74</v>
       </c>
       <c r="K3">
-        <v>155.36000000000001</v>
+        <v>112.04</v>
       </c>
       <c r="L3">
-        <v>147.32</v>
+        <v>109.31</v>
       </c>
       <c r="M3">
         <f t="shared" ref="M3:M20" si="0">L3/2</f>
-        <v>73.66</v>
+        <v>54.655000000000001</v>
       </c>
       <c r="N3">
         <v>95</v>
@@ -3355,41 +3355,41 @@
         <v>100</v>
       </c>
       <c r="B4">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C4">
-        <v>231.68</v>
+        <v>131.96</v>
       </c>
       <c r="D4">
-        <v>218.22</v>
+        <v>129</v>
       </c>
       <c r="E4">
-        <v>202.66</v>
+        <v>125.98</v>
       </c>
       <c r="F4">
-        <v>189.03</v>
+        <v>121.9</v>
       </c>
       <c r="G4">
-        <v>174.4</v>
+        <v>117.4</v>
       </c>
       <c r="H4">
-        <v>159.21</v>
+        <v>113.42</v>
       </c>
       <c r="I4">
-        <v>144.66999999999999</v>
+        <v>109.84</v>
       </c>
       <c r="J4">
-        <v>131.75</v>
+        <v>106.28</v>
       </c>
       <c r="K4">
-        <v>120.1</v>
+        <v>102.62</v>
       </c>
       <c r="L4">
-        <v>109.26</v>
+        <v>98.87</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>54.63</v>
+        <v>49.435000000000002</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -3437,41 +3437,41 @@
         <v>105</v>
       </c>
       <c r="B5">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C5">
-        <v>225.74</v>
+        <v>130.47</v>
       </c>
       <c r="D5">
-        <v>208.03</v>
+        <v>126.08</v>
       </c>
       <c r="E5">
-        <v>188.49</v>
+        <v>121.92</v>
       </c>
       <c r="F5">
-        <v>170.82</v>
+        <v>116.89</v>
       </c>
       <c r="G5">
-        <v>152.12</v>
+        <v>111.43</v>
       </c>
       <c r="H5">
-        <v>133.12</v>
+        <v>106.51</v>
       </c>
       <c r="I5">
-        <v>115.46</v>
+        <v>101.98</v>
       </c>
       <c r="J5">
-        <v>99.6</v>
+        <v>97.46</v>
       </c>
       <c r="K5">
-        <v>85.07</v>
+        <v>92.8</v>
       </c>
       <c r="L5">
-        <v>71.78</v>
+        <v>88.01</v>
       </c>
       <c r="M5">
         <f t="shared" si="0"/>
-        <v>35.89</v>
+        <v>44.005000000000003</v>
       </c>
       <c r="N5">
         <v>105</v>
@@ -3519,41 +3519,41 @@
         <v>110</v>
       </c>
       <c r="B6">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C6">
-        <v>219.92</v>
+        <v>129.02000000000001</v>
       </c>
       <c r="D6">
-        <v>197.99</v>
+        <v>123.21</v>
       </c>
       <c r="E6">
-        <v>174.53</v>
+        <v>117.84</v>
       </c>
       <c r="F6">
-        <v>152.9</v>
+        <v>111.92</v>
       </c>
       <c r="G6">
-        <v>130.43</v>
+        <v>105.5</v>
       </c>
       <c r="H6">
-        <v>107.82</v>
+        <v>99.59</v>
       </c>
       <c r="I6">
-        <v>86.98</v>
+        <v>94.06</v>
       </c>
       <c r="J6">
-        <v>68.05</v>
+        <v>88.56</v>
       </c>
       <c r="K6">
-        <v>50.89</v>
+        <v>82.95</v>
       </c>
       <c r="L6">
-        <v>35.299999999999997</v>
+        <v>77.209999999999994</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>17.649999999999999</v>
+        <v>38.604999999999997</v>
       </c>
       <c r="N6">
         <v>110</v>
@@ -3601,41 +3601,41 @@
         <v>115</v>
       </c>
       <c r="B7">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C7">
-        <v>214.26</v>
+        <v>127.62</v>
       </c>
       <c r="D7">
-        <v>188.11</v>
+        <v>120.41</v>
       </c>
       <c r="E7">
-        <v>160.88999999999999</v>
+        <v>113.78</v>
       </c>
       <c r="F7">
-        <v>135.41</v>
+        <v>107</v>
       </c>
       <c r="G7">
-        <v>109.39</v>
+        <v>99.69</v>
       </c>
       <c r="H7">
-        <v>83.4</v>
+        <v>92.8</v>
       </c>
       <c r="I7">
-        <v>59.44</v>
+        <v>86.28</v>
       </c>
       <c r="J7">
-        <v>37.72</v>
+        <v>79.819999999999993</v>
       </c>
       <c r="K7">
-        <v>18.22</v>
+        <v>73.290000000000006</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>66.66</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="N7">
         <v>115</v>
@@ -3683,41 +3683,41 @@
         <v>120</v>
       </c>
       <c r="B8">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C8">
-        <v>208.81</v>
+        <v>126.27</v>
       </c>
       <c r="D8">
-        <v>178.32</v>
+        <v>117.72</v>
       </c>
       <c r="E8">
-        <v>147.62</v>
+        <v>109.81</v>
       </c>
       <c r="F8">
-        <v>118.41</v>
+        <v>102.13</v>
       </c>
       <c r="G8">
-        <v>89</v>
+        <v>94.01</v>
       </c>
       <c r="H8">
-        <v>59.84</v>
+        <v>86.18</v>
       </c>
       <c r="I8">
-        <v>32.99</v>
+        <v>78.709999999999994</v>
       </c>
       <c r="J8">
-        <v>8.85</v>
+        <v>71.31</v>
       </c>
       <c r="K8">
-        <v>-13.24</v>
+        <v>63.89</v>
       </c>
       <c r="L8">
-        <v>-34.26</v>
+        <v>56.42</v>
       </c>
       <c r="M8">
         <f t="shared" si="0"/>
-        <v>-17.13</v>
+        <v>28.21</v>
       </c>
       <c r="N8">
         <v>120</v>
@@ -3765,41 +3765,41 @@
         <v>125</v>
       </c>
       <c r="B9">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C9">
-        <v>203.62</v>
+        <v>124.99</v>
       </c>
       <c r="D9">
-        <v>168.54</v>
+        <v>115.15</v>
       </c>
       <c r="E9">
-        <v>134.66999999999999</v>
+        <v>105.98</v>
       </c>
       <c r="F9">
-        <v>101.98</v>
+        <v>97.27</v>
       </c>
       <c r="G9">
-        <v>69.22</v>
+        <v>88.44</v>
       </c>
       <c r="H9">
-        <v>37.11</v>
+        <v>79.739999999999995</v>
       </c>
       <c r="I9">
-        <v>7.62</v>
+        <v>71.39</v>
       </c>
       <c r="J9">
-        <v>-19.09</v>
+        <v>63.1</v>
       </c>
       <c r="K9">
-        <v>-44</v>
+        <v>54.81</v>
       </c>
       <c r="L9">
-        <v>-67.86</v>
+        <v>46.5</v>
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
-        <v>-33.93</v>
+        <v>23.25</v>
       </c>
       <c r="N9">
         <v>125</v>
@@ -3847,41 +3847,41 @@
         <v>130</v>
       </c>
       <c r="B10">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C10">
-        <v>198.71</v>
+        <v>123.78</v>
       </c>
       <c r="D10">
-        <v>158.91999999999999</v>
+        <v>112.72</v>
       </c>
       <c r="E10">
-        <v>121.89</v>
+        <v>102.35</v>
       </c>
       <c r="F10">
-        <v>86.05</v>
+        <v>92.51</v>
       </c>
       <c r="G10">
-        <v>50.02</v>
+        <v>82.89</v>
       </c>
       <c r="H10">
-        <v>14.99</v>
+        <v>73.42</v>
       </c>
       <c r="I10">
-        <v>-17.12</v>
+        <v>64.28</v>
       </c>
       <c r="J10">
-        <v>-46.58</v>
+        <v>55.17</v>
       </c>
       <c r="K10">
-        <v>-74.260000000000005</v>
+        <v>46.05</v>
       </c>
       <c r="L10">
-        <v>-100.88</v>
+        <v>36.93</v>
       </c>
       <c r="M10">
         <f t="shared" si="0"/>
-        <v>-50.44</v>
+        <v>18.465</v>
       </c>
       <c r="N10">
         <v>130</v>
@@ -3929,41 +3929,41 @@
         <v>135</v>
       </c>
       <c r="B11">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C11">
-        <v>194.14</v>
+        <v>122.66</v>
       </c>
       <c r="D11">
-        <v>149.71</v>
+        <v>110.46</v>
       </c>
       <c r="E11">
-        <v>108.98</v>
+        <v>98.93</v>
       </c>
       <c r="F11">
-        <v>70.47</v>
+        <v>87.96</v>
       </c>
       <c r="G11">
-        <v>31.51</v>
+        <v>77.349999999999994</v>
       </c>
       <c r="H11">
-        <v>-6.38</v>
+        <v>67.08</v>
       </c>
       <c r="I11">
-        <v>-41.42</v>
+        <v>57.23</v>
       </c>
       <c r="J11">
-        <v>-73.86</v>
+        <v>47.42</v>
       </c>
       <c r="K11">
-        <v>-104.51</v>
+        <v>37.56</v>
       </c>
       <c r="L11">
-        <v>-133.94999999999999</v>
+        <v>27.67</v>
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
-        <v>-66.974999999999994</v>
+        <v>13.835000000000001</v>
       </c>
       <c r="N11">
         <v>135</v>
@@ -4011,41 +4011,41 @@
         <v>140</v>
       </c>
       <c r="B12">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C12">
-        <v>189.94</v>
+        <v>121.63</v>
       </c>
       <c r="D12">
-        <v>141.13</v>
+        <v>108.38</v>
       </c>
       <c r="E12">
-        <v>96.02</v>
+        <v>95.78</v>
       </c>
       <c r="F12">
-        <v>54.85</v>
+        <v>83.73</v>
       </c>
       <c r="G12">
-        <v>13.64</v>
+        <v>72.040000000000006</v>
       </c>
       <c r="H12">
-        <v>-26.91</v>
+        <v>60.73</v>
       </c>
       <c r="I12">
-        <v>-65.150000000000006</v>
+        <v>50.04</v>
       </c>
       <c r="J12">
-        <v>-101.03</v>
+        <v>39.65</v>
       </c>
       <c r="K12">
-        <v>-134.85</v>
+        <v>29.22</v>
       </c>
       <c r="L12">
-        <v>-165.73</v>
+        <v>18.73</v>
       </c>
       <c r="M12">
         <f t="shared" si="0"/>
-        <v>-82.864999999999995</v>
+        <v>9.3650000000000002</v>
       </c>
       <c r="N12">
         <v>140</v>
@@ -4093,41 +4093,41 @@
         <v>145</v>
       </c>
       <c r="B13">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C13">
-        <v>186.15</v>
+        <v>120.71</v>
       </c>
       <c r="D13">
-        <v>133.30000000000001</v>
+        <v>106.5</v>
       </c>
       <c r="E13">
-        <v>83.92</v>
+        <v>92.9</v>
       </c>
       <c r="F13">
-        <v>38.729999999999997</v>
+        <v>79.849999999999994</v>
       </c>
       <c r="G13">
-        <v>-4.63</v>
+        <v>67.150000000000006</v>
       </c>
       <c r="H13">
-        <v>-47.22</v>
+        <v>54.8</v>
       </c>
       <c r="I13">
-        <v>-88.4</v>
+        <v>42.96</v>
       </c>
       <c r="J13">
-        <v>-127.5</v>
+        <v>31.68</v>
       </c>
       <c r="K13">
-        <v>-162.72999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="L13">
-        <v>-192.77</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="M13">
         <f t="shared" si="0"/>
-        <v>-96.385000000000005</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="N13">
         <v>145</v>
@@ -4175,41 +4175,41 @@
         <v>150</v>
       </c>
       <c r="B14">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C14">
-        <v>182.79</v>
+        <v>119.89</v>
       </c>
       <c r="D14">
-        <v>126.33</v>
+        <v>104.84</v>
       </c>
       <c r="E14">
-        <v>73.069999999999993</v>
+        <v>90.35</v>
       </c>
       <c r="F14">
-        <v>23.49</v>
+        <v>76.39</v>
       </c>
       <c r="G14">
-        <v>-23.32</v>
+        <v>62.77</v>
       </c>
       <c r="H14">
-        <v>-68.680000000000007</v>
+        <v>49.47</v>
       </c>
       <c r="I14">
-        <v>-112.36</v>
+        <v>36.54</v>
       </c>
       <c r="J14">
-        <v>-152.63999999999999</v>
+        <v>24.16</v>
       </c>
       <c r="K14">
-        <v>-187.63</v>
+        <v>12.15</v>
       </c>
       <c r="L14">
-        <v>-218.51</v>
+        <v>0.35</v>
       </c>
       <c r="M14">
         <f t="shared" si="0"/>
-        <v>-109.255</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="N14">
         <v>150</v>
@@ -4257,41 +4257,41 @@
         <v>155</v>
       </c>
       <c r="B15">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C15">
-        <v>179.91</v>
+        <v>119.19</v>
       </c>
       <c r="D15">
-        <v>120.27</v>
+        <v>103.42</v>
       </c>
       <c r="E15">
-        <v>63.69</v>
+        <v>88.13</v>
       </c>
       <c r="F15">
-        <v>10.16</v>
+        <v>73.38</v>
       </c>
       <c r="G15">
-        <v>-39.82</v>
+        <v>58.96</v>
       </c>
       <c r="H15">
-        <v>-88.14</v>
+        <v>44.83</v>
       </c>
       <c r="I15">
-        <v>-133.94</v>
+        <v>30.99</v>
       </c>
       <c r="J15">
-        <v>-174.82</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="K15">
-        <v>-212.16</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
-        <v>-245.29</v>
+        <v>-7.87</v>
       </c>
       <c r="M15">
         <f t="shared" si="0"/>
-        <v>-122.645</v>
+        <v>-3.9350000000000001</v>
       </c>
       <c r="N15">
         <v>155</v>
@@ -4339,41 +4339,41 @@
         <v>160</v>
       </c>
       <c r="B16">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C16">
-        <v>177.52</v>
+        <v>118.61</v>
       </c>
       <c r="D16">
-        <v>115.21</v>
+        <v>102.24</v>
       </c>
       <c r="E16">
-        <v>56.09</v>
+        <v>86.3</v>
       </c>
       <c r="F16">
-        <v>-0.61</v>
+        <v>70.86</v>
       </c>
       <c r="G16">
-        <v>-53.94</v>
+        <v>55.79</v>
       </c>
       <c r="H16">
-        <v>-104.9</v>
+        <v>41.03</v>
       </c>
       <c r="I16">
-        <v>-151.44999999999999</v>
+        <v>26.56</v>
       </c>
       <c r="J16">
-        <v>-193.62</v>
+        <v>12.35</v>
       </c>
       <c r="K16">
-        <v>-233.85</v>
+        <v>-1.51</v>
       </c>
       <c r="L16">
-        <v>-270.18</v>
+        <v>-14.89</v>
       </c>
       <c r="M16">
         <f t="shared" si="0"/>
-        <v>-135.09</v>
+        <v>-7.4450000000000003</v>
       </c>
       <c r="N16">
         <v>160</v>
@@ -4421,41 +4421,41 @@
         <v>165</v>
       </c>
       <c r="B17">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C17">
-        <v>175.66</v>
+        <v>118.15</v>
       </c>
       <c r="D17">
-        <v>111.22</v>
+        <v>101.32</v>
       </c>
       <c r="E17">
-        <v>50.26</v>
+        <v>84.85</v>
       </c>
       <c r="F17">
-        <v>-8.83</v>
+        <v>68.88</v>
       </c>
       <c r="G17">
-        <v>-65.540000000000006</v>
+        <v>53.34</v>
       </c>
       <c r="H17">
-        <v>-118.72</v>
+        <v>38.130000000000003</v>
       </c>
       <c r="I17">
-        <v>-165.91</v>
+        <v>23.13</v>
       </c>
       <c r="J17">
-        <v>-209.48</v>
+        <v>8.31</v>
       </c>
       <c r="K17">
-        <v>-251.72</v>
+        <v>-6.3</v>
       </c>
       <c r="L17">
-        <v>-292.2</v>
+        <v>-20.57</v>
       </c>
       <c r="M17">
         <f t="shared" si="0"/>
-        <v>-146.1</v>
+        <v>-10.285</v>
       </c>
       <c r="N17">
         <v>165</v>
@@ -4503,41 +4503,41 @@
         <v>170</v>
       </c>
       <c r="B18">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C18">
-        <v>174.34</v>
+        <v>117.82</v>
       </c>
       <c r="D18">
-        <v>108.42</v>
+        <v>100.66</v>
       </c>
       <c r="E18">
-        <v>46.04</v>
+        <v>83.81</v>
       </c>
       <c r="F18">
-        <v>-14.69</v>
+        <v>67.489999999999995</v>
       </c>
       <c r="G18">
-        <v>-73.67</v>
+        <v>51.62</v>
       </c>
       <c r="H18">
-        <v>-129.18</v>
+        <v>36.04</v>
       </c>
       <c r="I18">
-        <v>-177.48</v>
+        <v>20.65</v>
       </c>
       <c r="J18">
-        <v>-222.44</v>
+        <v>5.42</v>
       </c>
       <c r="K18">
-        <v>-266.12</v>
+        <v>-9.66</v>
       </c>
       <c r="L18">
-        <v>-309</v>
+        <v>-24.5</v>
       </c>
       <c r="M18">
         <f t="shared" si="0"/>
-        <v>-154.5</v>
+        <v>-12.25</v>
       </c>
       <c r="N18">
         <v>170</v>
@@ -4585,41 +4585,41 @@
         <v>175</v>
       </c>
       <c r="B19">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C19">
-        <v>173.56</v>
+        <v>117.62</v>
       </c>
       <c r="D19">
-        <v>106.8</v>
+        <v>100.27</v>
       </c>
       <c r="E19">
-        <v>43.44</v>
+        <v>83.17</v>
       </c>
       <c r="F19">
-        <v>-18.36</v>
+        <v>66.680000000000007</v>
       </c>
       <c r="G19">
-        <v>-78.42</v>
+        <v>50.6</v>
       </c>
       <c r="H19">
-        <v>-135.13</v>
+        <v>34.770000000000003</v>
       </c>
       <c r="I19">
-        <v>-185.28</v>
+        <v>19.12</v>
       </c>
       <c r="J19">
-        <v>-231.85</v>
+        <v>3.63</v>
       </c>
       <c r="K19">
-        <v>-276.83999999999997</v>
+        <v>-11.73</v>
       </c>
       <c r="L19">
-        <v>-320.95999999999998</v>
+        <v>-26.85</v>
       </c>
       <c r="M19">
         <f t="shared" si="0"/>
-        <v>-160.47999999999999</v>
+        <v>-13.425000000000001</v>
       </c>
       <c r="N19">
         <v>175</v>
@@ -4667,41 +4667,41 @@
         <v>180</v>
       </c>
       <c r="B20">
-        <v>243.64</v>
+        <v>135.05000000000001</v>
       </c>
       <c r="C20">
-        <v>173.3</v>
+        <v>117.55</v>
       </c>
       <c r="D20">
-        <v>106.26</v>
+        <v>100.14</v>
       </c>
       <c r="E20">
-        <v>42.52</v>
+        <v>82.95</v>
       </c>
       <c r="F20">
-        <v>-19.690000000000001</v>
+        <v>66.430000000000007</v>
       </c>
       <c r="G20">
-        <v>-80.02</v>
+        <v>50.27</v>
       </c>
       <c r="H20">
-        <v>-136.93</v>
+        <v>34.33</v>
       </c>
       <c r="I20">
-        <v>-187.6</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="J20">
-        <v>-235.55</v>
+        <v>2.98</v>
       </c>
       <c r="K20">
-        <v>-281.76</v>
+        <v>-12.44</v>
       </c>
       <c r="L20">
-        <v>-326.05</v>
+        <v>-27.64</v>
       </c>
       <c r="M20">
         <f t="shared" si="0"/>
-        <v>-163.02500000000001</v>
+        <v>-13.82</v>
       </c>
       <c r="N20">
         <v>180</v>
@@ -6224,54 +6224,54 @@
       </c>
       <c r="B43">
         <f>B2-B23</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:L43" si="2">C2-C23</f>
-        <v>101.57</v>
+        <v>-7.1700000000000159</v>
       </c>
       <c r="D43">
         <f t="shared" si="2"/>
-        <v>97.13</v>
+        <v>-6.7700000000000102</v>
       </c>
       <c r="E43">
         <f t="shared" si="2"/>
-        <v>90.809999999999974</v>
+        <v>-5.5400000000000205</v>
       </c>
       <c r="F43">
         <f t="shared" si="2"/>
-        <v>86.739999999999981</v>
+        <v>-5.5</v>
       </c>
       <c r="G43">
         <f t="shared" si="2"/>
-        <v>82.039999999999992</v>
+        <v>-6.0900000000000034</v>
       </c>
       <c r="H43">
         <f t="shared" si="2"/>
-        <v>77.38</v>
+        <v>-6.1099999999999994</v>
       </c>
       <c r="I43">
         <f t="shared" si="2"/>
-        <v>72.389999999999986</v>
+        <v>-5.8600000000000136</v>
       </c>
       <c r="J43">
         <f t="shared" si="2"/>
-        <v>67.84</v>
+        <v>-5.480000000000004</v>
       </c>
       <c r="K43">
         <f t="shared" si="2"/>
-        <v>65.250000000000014</v>
+        <v>-4.0400000000000063</v>
       </c>
       <c r="L43">
         <f t="shared" si="2"/>
-        <v>62.379999999999995</v>
+        <v>-3.6700000000000017</v>
       </c>
       <c r="O43">
         <f>O2-O23</f>
         <v>0.02</v>
       </c>
       <c r="P43">
-        <f t="shared" ref="P43:Y43" si="3">P2-P23</f>
+        <f t="shared" ref="P43:X43" si="3">P2-P23</f>
         <v>126.13999999999999</v>
       </c>
       <c r="Q43">
@@ -6317,47 +6317,47 @@
       </c>
       <c r="B44">
         <f t="shared" ref="B44:L44" si="4">B3-B24</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C44">
         <f t="shared" si="4"/>
-        <v>97.53</v>
+        <v>-6.6999999999999886</v>
       </c>
       <c r="D44">
         <f t="shared" si="4"/>
-        <v>90.070000000000022</v>
+        <v>-6.4899999999999807</v>
       </c>
       <c r="E44">
         <f t="shared" si="4"/>
-        <v>80.5</v>
+        <v>-6.210000000000008</v>
       </c>
       <c r="F44">
         <f t="shared" si="4"/>
-        <v>73.669999999999987</v>
+        <v>-6.4399999999999977</v>
       </c>
       <c r="G44">
         <f t="shared" si="4"/>
-        <v>66.52000000000001</v>
+        <v>-6.6599999999999966</v>
       </c>
       <c r="H44">
         <f t="shared" si="4"/>
-        <v>58.760000000000005</v>
+        <v>-6.480000000000004</v>
       </c>
       <c r="I44">
         <f t="shared" si="4"/>
-        <v>51.040000000000006</v>
+        <v>-5.7999999999999972</v>
       </c>
       <c r="J44">
         <f t="shared" si="4"/>
-        <v>43.75</v>
+        <v>-5.730000000000004</v>
       </c>
       <c r="K44">
         <f t="shared" si="4"/>
-        <v>38.15000000000002</v>
+        <v>-5.1699999999999875</v>
       </c>
       <c r="L44">
         <f t="shared" si="4"/>
-        <v>33.36</v>
+        <v>-4.6499999999999915</v>
       </c>
       <c r="O44">
         <f t="shared" ref="O44:Y44" si="5">O3-O24</f>
@@ -6410,47 +6410,47 @@
       </c>
       <c r="B45">
         <f t="shared" ref="B45:L45" si="6">B4-B25</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C45">
         <f t="shared" si="6"/>
-        <v>93.230000000000018</v>
+        <v>-6.4899999999999807</v>
       </c>
       <c r="D45">
         <f t="shared" si="6"/>
-        <v>82.889999999999986</v>
+        <v>-6.3300000000000125</v>
       </c>
       <c r="E45">
         <f t="shared" si="6"/>
-        <v>70.900000000000006</v>
+        <v>-5.7799999999999869</v>
       </c>
       <c r="F45">
         <f t="shared" si="6"/>
-        <v>60.879999999999995</v>
+        <v>-6.25</v>
       </c>
       <c r="G45">
         <f t="shared" si="6"/>
-        <v>50.490000000000009</v>
+        <v>-6.5099999999999909</v>
       </c>
       <c r="H45">
         <f t="shared" si="6"/>
-        <v>38.460000000000008</v>
+        <v>-7.3299999999999983</v>
       </c>
       <c r="I45">
         <f t="shared" si="6"/>
-        <v>28.259999999999991</v>
+        <v>-6.5699999999999932</v>
       </c>
       <c r="J45">
         <f t="shared" si="6"/>
-        <v>19.11</v>
+        <v>-6.3599999999999994</v>
       </c>
       <c r="K45">
         <f t="shared" si="6"/>
-        <v>11.22999999999999</v>
+        <v>-6.25</v>
       </c>
       <c r="L45">
         <f t="shared" si="6"/>
-        <v>4.1600000000000108</v>
+        <v>-6.2299999999999898</v>
       </c>
       <c r="O45">
         <f t="shared" ref="O45:Y45" si="7">O4-O25</f>
@@ -6503,47 +6503,47 @@
       </c>
       <c r="B46">
         <f t="shared" ref="B46:L46" si="8">B5-B26</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C46">
         <f t="shared" si="8"/>
-        <v>89.100000000000023</v>
+        <v>-6.1699999999999875</v>
       </c>
       <c r="D46">
         <f t="shared" si="8"/>
-        <v>75.930000000000007</v>
+        <v>-6.019999999999996</v>
       </c>
       <c r="E46">
         <f t="shared" si="8"/>
-        <v>61.040000000000006</v>
+        <v>-5.5300000000000011</v>
       </c>
       <c r="F46">
         <f t="shared" si="8"/>
-        <v>47.929999999999993</v>
+        <v>-6</v>
       </c>
       <c r="G46">
         <f t="shared" si="8"/>
-        <v>34.200000000000003</v>
+        <v>-6.4899999999999949</v>
       </c>
       <c r="H46">
         <f t="shared" si="8"/>
-        <v>19.78</v>
+        <v>-6.8299999999999983</v>
       </c>
       <c r="I46">
         <f t="shared" si="8"/>
-        <v>6.2999999999999972</v>
+        <v>-7.1799999999999926</v>
       </c>
       <c r="J46">
         <f t="shared" si="8"/>
-        <v>-5.2800000000000011</v>
+        <v>-7.4200000000000017</v>
       </c>
       <c r="K46">
         <f t="shared" si="8"/>
-        <v>-15</v>
+        <v>-7.269999999999996</v>
       </c>
       <c r="L46">
         <f t="shared" si="8"/>
-        <v>-24.010000000000005</v>
+        <v>-7.7800000000000011</v>
       </c>
       <c r="O46">
         <f t="shared" ref="O46:Y46" si="9">O5-O26</f>
@@ -6596,47 +6596,47 @@
       </c>
       <c r="B47">
         <f t="shared" ref="B47:L47" si="10">B6-B27</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C47">
         <f t="shared" si="10"/>
-        <v>84.839999999999975</v>
+        <v>-6.0600000000000023</v>
       </c>
       <c r="D47">
         <f t="shared" si="10"/>
-        <v>69.22</v>
+        <v>-5.5600000000000165</v>
       </c>
       <c r="E47">
         <f t="shared" si="10"/>
-        <v>51.33</v>
+        <v>-5.3599999999999994</v>
       </c>
       <c r="F47">
         <f t="shared" si="10"/>
-        <v>35.260000000000005</v>
+        <v>-5.7199999999999989</v>
       </c>
       <c r="G47">
         <f t="shared" si="10"/>
-        <v>18.300000000000011</v>
+        <v>-6.6299999999999955</v>
       </c>
       <c r="H47">
         <f t="shared" si="10"/>
-        <v>1.6299999999999955</v>
+        <v>-6.5999999999999943</v>
       </c>
       <c r="I47">
         <f t="shared" si="10"/>
-        <v>-14.459999999999994</v>
+        <v>-7.3799999999999955</v>
       </c>
       <c r="J47">
         <f t="shared" si="10"/>
-        <v>-29.14</v>
+        <v>-8.6299999999999955</v>
       </c>
       <c r="K47">
         <f t="shared" si="10"/>
-        <v>-40.989999999999995</v>
+        <v>-8.9299999999999926</v>
       </c>
       <c r="L47">
         <f t="shared" si="10"/>
-        <v>-50.740000000000009</v>
+        <v>-8.8300000000000125</v>
       </c>
       <c r="O47">
         <f t="shared" ref="O47:Y47" si="11">O6-O27</f>
@@ -6689,47 +6689,47 @@
       </c>
       <c r="B48">
         <f t="shared" ref="B48:L48" si="12">B7-B28</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C48">
         <f t="shared" si="12"/>
-        <v>81.03</v>
+        <v>-5.6099999999999852</v>
       </c>
       <c r="D48">
         <f t="shared" si="12"/>
-        <v>62.160000000000011</v>
+        <v>-5.5400000000000063</v>
       </c>
       <c r="E48">
         <f t="shared" si="12"/>
-        <v>41.719999999999985</v>
+        <v>-5.3900000000000006</v>
       </c>
       <c r="F48">
         <f t="shared" si="12"/>
-        <v>22.78</v>
+        <v>-5.6299999999999955</v>
       </c>
       <c r="G48">
         <f t="shared" si="12"/>
-        <v>3.1899999999999977</v>
+        <v>-6.5100000000000051</v>
       </c>
       <c r="H48">
         <f t="shared" si="12"/>
-        <v>-16.519999999999996</v>
+        <v>-7.1200000000000045</v>
       </c>
       <c r="I48">
         <f t="shared" si="12"/>
-        <v>-34.019999999999996</v>
+        <v>-7.1799999999999926</v>
       </c>
       <c r="J48">
         <f t="shared" si="12"/>
-        <v>-51.31</v>
+        <v>-9.210000000000008</v>
       </c>
       <c r="K48">
         <f t="shared" si="12"/>
-        <v>-64.48</v>
+        <v>-9.4099999999999966</v>
       </c>
       <c r="L48">
         <f t="shared" si="12"/>
-        <v>-76.37</v>
+        <v>-9.710000000000008</v>
       </c>
       <c r="O48">
         <f t="shared" ref="O48:Y48" si="13">O7-O28</f>
@@ -6782,47 +6782,47 @@
       </c>
       <c r="B49">
         <f t="shared" ref="B49:L49" si="14">B8-B29</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C49">
         <f t="shared" si="14"/>
-        <v>76.88</v>
+        <v>-5.6600000000000108</v>
       </c>
       <c r="D49">
         <f t="shared" si="14"/>
-        <v>55.419999999999987</v>
+        <v>-5.1800000000000068</v>
       </c>
       <c r="E49">
         <f t="shared" si="14"/>
-        <v>32.240000000000009</v>
+        <v>-5.5699999999999932</v>
       </c>
       <c r="F49">
         <f t="shared" si="14"/>
-        <v>10.659999999999997</v>
+        <v>-5.6200000000000045</v>
       </c>
       <c r="G49">
         <f t="shared" si="14"/>
-        <v>-11.569999999999993</v>
+        <v>-6.5599999999999881</v>
       </c>
       <c r="H49">
         <f t="shared" si="14"/>
-        <v>-33.340000000000003</v>
+        <v>-7</v>
       </c>
       <c r="I49">
         <f t="shared" si="14"/>
-        <v>-53.219999999999992</v>
+        <v>-7.5</v>
       </c>
       <c r="J49">
         <f t="shared" si="14"/>
-        <v>-71.11</v>
+        <v>-8.6499999999999915</v>
       </c>
       <c r="K49">
         <f t="shared" si="14"/>
-        <v>-87.36</v>
+        <v>-10.230000000000004</v>
       </c>
       <c r="L49">
         <f t="shared" si="14"/>
-        <v>-101.03999999999999</v>
+        <v>-10.36</v>
       </c>
       <c r="O49">
         <f t="shared" ref="O49:Y49" si="15">O8-O29</f>
@@ -6875,47 +6875,47 @@
       </c>
       <c r="B50">
         <f t="shared" ref="B50:L50" si="16">B9-B30</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C50">
         <f t="shared" si="16"/>
-        <v>73.789999999999992</v>
+        <v>-4.8400000000000176</v>
       </c>
       <c r="D50">
         <f t="shared" si="16"/>
-        <v>48.3</v>
+        <v>-5.0899999999999892</v>
       </c>
       <c r="E50">
         <f t="shared" si="16"/>
-        <v>23.659999999999982</v>
+        <v>-5.0300000000000011</v>
       </c>
       <c r="F50">
         <f t="shared" si="16"/>
-        <v>-0.61999999999999034</v>
+        <v>-5.3299999999999983</v>
       </c>
       <c r="G50">
         <f t="shared" si="16"/>
-        <v>-25.370000000000005</v>
+        <v>-6.1500000000000057</v>
       </c>
       <c r="H50">
         <f t="shared" si="16"/>
-        <v>-49.34</v>
+        <v>-6.710000000000008</v>
       </c>
       <c r="I50">
         <f t="shared" si="16"/>
-        <v>-71.099999999999994</v>
+        <v>-7.3299999999999983</v>
       </c>
       <c r="J50">
         <f t="shared" si="16"/>
-        <v>-90.13000000000001</v>
+        <v>-7.9400000000000048</v>
       </c>
       <c r="K50">
         <f t="shared" si="16"/>
-        <v>-108.77</v>
+        <v>-9.9599999999999937</v>
       </c>
       <c r="L50">
         <f t="shared" si="16"/>
-        <v>-125.66</v>
+        <v>-11.299999999999997</v>
       </c>
       <c r="O50">
         <f t="shared" ref="O50:Y50" si="17">O9-O30</f>
@@ -6968,47 +6968,47 @@
       </c>
       <c r="B51">
         <f t="shared" ref="B51:L51" si="18">B10-B31</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C51">
         <f t="shared" si="18"/>
-        <v>69.960000000000008</v>
+        <v>-4.9699999999999989</v>
       </c>
       <c r="D51">
         <f t="shared" si="18"/>
-        <v>41.489999999999981</v>
+        <v>-4.710000000000008</v>
       </c>
       <c r="E51">
         <f t="shared" si="18"/>
-        <v>15.299999999999997</v>
+        <v>-4.2400000000000091</v>
       </c>
       <c r="F51">
         <f t="shared" si="18"/>
-        <v>-11.260000000000005</v>
+        <v>-4.7999999999999972</v>
       </c>
       <c r="G51">
         <f t="shared" si="18"/>
-        <v>-38.589999999999996</v>
+        <v>-5.7199999999999989</v>
       </c>
       <c r="H51">
         <f t="shared" si="18"/>
-        <v>-65</v>
+        <v>-6.5699999999999932</v>
       </c>
       <c r="I51">
         <f t="shared" si="18"/>
-        <v>-88.37</v>
+        <v>-6.9699999999999989</v>
       </c>
       <c r="J51">
         <f t="shared" si="18"/>
-        <v>-109.31</v>
+        <v>-7.5599999999999952</v>
       </c>
       <c r="K51">
         <f t="shared" si="18"/>
-        <v>-129.14000000000001</v>
+        <v>-8.8300000000000054</v>
       </c>
       <c r="L51">
         <f t="shared" si="18"/>
-        <v>-148.41</v>
+        <v>-10.600000000000001</v>
       </c>
       <c r="O51">
         <f t="shared" ref="O51:Y51" si="19">O10-O31</f>
@@ -7061,47 +7061,47 @@
       </c>
       <c r="B52">
         <f t="shared" ref="B52:L52" si="20">B11-B32</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C52">
         <f t="shared" si="20"/>
-        <v>67.109999999999985</v>
+        <v>-4.3700000000000045</v>
       </c>
       <c r="D52">
         <f t="shared" si="20"/>
-        <v>35.840000000000003</v>
+        <v>-3.4100000000000108</v>
       </c>
       <c r="E52">
         <f t="shared" si="20"/>
-        <v>5.980000000000004</v>
+        <v>-4.0699999999999932</v>
       </c>
       <c r="F52">
         <f t="shared" si="20"/>
-        <v>-22.060000000000002</v>
+        <v>-4.5700000000000074</v>
       </c>
       <c r="G52">
         <f t="shared" si="20"/>
-        <v>-51.379999999999995</v>
+        <v>-5.5400000000000063</v>
       </c>
       <c r="H52">
         <f t="shared" si="20"/>
-        <v>-79.86</v>
+        <v>-6.4000000000000057</v>
       </c>
       <c r="I52">
         <f t="shared" si="20"/>
-        <v>-105.43</v>
+        <v>-6.7800000000000082</v>
       </c>
       <c r="J52">
         <f t="shared" si="20"/>
-        <v>-128.71</v>
+        <v>-7.43</v>
       </c>
       <c r="K52">
         <f t="shared" si="20"/>
-        <v>-150.21</v>
+        <v>-8.14</v>
       </c>
       <c r="L52">
         <f t="shared" si="20"/>
-        <v>-171.07</v>
+        <v>-9.4499999999999957</v>
       </c>
       <c r="O52">
         <f t="shared" ref="O52:Y52" si="21">O11-O32</f>
@@ -7154,47 +7154,47 @@
       </c>
       <c r="B53">
         <f t="shared" ref="B53:L53" si="22">B12-B33</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C53">
         <f t="shared" si="22"/>
-        <v>64.429999999999993</v>
+        <v>-3.8800000000000097</v>
       </c>
       <c r="D53">
         <f t="shared" si="22"/>
-        <v>29.209999999999994</v>
+        <v>-3.5400000000000063</v>
       </c>
       <c r="E53">
         <f t="shared" si="22"/>
-        <v>-3.5</v>
+        <v>-3.7399999999999949</v>
       </c>
       <c r="F53">
         <f t="shared" si="22"/>
-        <v>-33.499999999999993</v>
+        <v>-4.6199999999999903</v>
       </c>
       <c r="G53">
         <f t="shared" si="22"/>
-        <v>-63.790000000000006</v>
+        <v>-5.3900000000000006</v>
       </c>
       <c r="H53">
         <f t="shared" si="22"/>
-        <v>-93.8</v>
+        <v>-6.1600000000000037</v>
       </c>
       <c r="I53">
         <f t="shared" si="22"/>
-        <v>-121.88</v>
+        <v>-6.6899999999999977</v>
       </c>
       <c r="J53">
         <f t="shared" si="22"/>
-        <v>-148</v>
+        <v>-7.32</v>
       </c>
       <c r="K53">
         <f t="shared" si="22"/>
-        <v>-172.22</v>
+        <v>-8.1499999999999986</v>
       </c>
       <c r="L53">
         <f t="shared" si="22"/>
-        <v>-193.48</v>
+        <v>-9.02</v>
       </c>
       <c r="O53">
         <f t="shared" ref="O53:Y53" si="23">O12-O33</f>
@@ -7247,47 +7247,47 @@
       </c>
       <c r="B54">
         <f t="shared" ref="B54:L54" si="24">B13-B34</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C54">
         <f t="shared" si="24"/>
-        <v>61.650000000000006</v>
+        <v>-3.7900000000000063</v>
       </c>
       <c r="D54">
         <f t="shared" si="24"/>
-        <v>23.840000000000018</v>
+        <v>-2.9599999999999937</v>
       </c>
       <c r="E54">
         <f t="shared" si="24"/>
-        <v>-12.370000000000005</v>
+        <v>-3.3900000000000006</v>
       </c>
       <c r="F54">
         <f t="shared" si="24"/>
-        <v>-44.82</v>
+        <v>-3.7000000000000028</v>
       </c>
       <c r="G54">
         <f t="shared" si="24"/>
-        <v>-76.289999999999992</v>
+        <v>-4.5099999999999909</v>
       </c>
       <c r="H54">
         <f t="shared" si="24"/>
-        <v>-107.78</v>
+        <v>-5.7600000000000051</v>
       </c>
       <c r="I54">
         <f t="shared" si="24"/>
-        <v>-138.29000000000002</v>
+        <v>-6.93</v>
       </c>
       <c r="J54">
         <f t="shared" si="24"/>
-        <v>-166.48</v>
+        <v>-7.2999999999999972</v>
       </c>
       <c r="K54">
         <f t="shared" si="24"/>
-        <v>-191.23</v>
+        <v>-7.8999999999999986</v>
       </c>
       <c r="L54">
         <f t="shared" si="24"/>
-        <v>-211.43</v>
+        <v>-9.0400000000000009</v>
       </c>
       <c r="O54">
         <f t="shared" ref="O54:Y54" si="25">O13-O34</f>
@@ -7340,47 +7340,47 @@
       </c>
       <c r="B55">
         <f t="shared" ref="B55:L55" si="26">B14-B35</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C55">
         <f t="shared" si="26"/>
-        <v>59.44</v>
+        <v>-3.4599999999999937</v>
       </c>
       <c r="D55">
         <f t="shared" si="26"/>
-        <v>18.819999999999993</v>
+        <v>-2.6700000000000017</v>
       </c>
       <c r="E55">
         <f t="shared" si="26"/>
-        <v>-19.720000000000013</v>
+        <v>-2.4400000000000119</v>
       </c>
       <c r="F55">
         <f t="shared" si="26"/>
-        <v>-55.72</v>
+        <v>-2.8199999999999932</v>
       </c>
       <c r="G55">
         <f t="shared" si="26"/>
-        <v>-90.03</v>
+        <v>-3.9399999999999906</v>
       </c>
       <c r="H55">
         <f t="shared" si="26"/>
-        <v>-123.41</v>
+        <v>-5.259999999999998</v>
       </c>
       <c r="I55">
         <f t="shared" si="26"/>
-        <v>-155.29</v>
+        <v>-6.3900000000000006</v>
       </c>
       <c r="J55">
         <f t="shared" si="26"/>
-        <v>-184.04999999999998</v>
+        <v>-7.25</v>
       </c>
       <c r="K55">
         <f t="shared" si="26"/>
-        <v>-207.89</v>
+        <v>-8.1100000000000012</v>
       </c>
       <c r="L55">
         <f t="shared" si="26"/>
-        <v>-227.7</v>
+        <v>-8.84</v>
       </c>
       <c r="O55">
         <f t="shared" ref="O55:Y55" si="27">O14-O35</f>
@@ -7433,47 +7433,47 @@
       </c>
       <c r="B56">
         <f t="shared" ref="B56:L56" si="28">B15-B36</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C56">
         <f t="shared" si="28"/>
-        <v>57.92</v>
+        <v>-2.7999999999999972</v>
       </c>
       <c r="D56">
         <f t="shared" si="28"/>
-        <v>14.429999999999993</v>
+        <v>-2.4200000000000017</v>
       </c>
       <c r="E56">
         <f t="shared" si="28"/>
-        <v>-27.010000000000005</v>
+        <v>-2.5700000000000074</v>
       </c>
       <c r="F56">
         <f t="shared" si="28"/>
-        <v>-65.89</v>
+        <v>-2.6700000000000017</v>
       </c>
       <c r="G56">
         <f t="shared" si="28"/>
-        <v>-102.42</v>
+        <v>-3.6400000000000006</v>
       </c>
       <c r="H56">
         <f t="shared" si="28"/>
-        <v>-137.55000000000001</v>
+        <v>-4.5799999999999983</v>
       </c>
       <c r="I56">
         <f t="shared" si="28"/>
-        <v>-170.44</v>
+        <v>-5.5100000000000016</v>
       </c>
       <c r="J56">
         <f t="shared" si="28"/>
-        <v>-199.18</v>
+        <v>-6.759999999999998</v>
       </c>
       <c r="K56">
         <f t="shared" si="28"/>
-        <v>-224.4</v>
+        <v>-7.54</v>
       </c>
       <c r="L56">
         <f t="shared" si="28"/>
-        <v>-245.79999999999998</v>
+        <v>-8.3800000000000008</v>
       </c>
       <c r="O56">
         <f t="shared" ref="O56:Y56" si="29">O15-O36</f>
@@ -7526,47 +7526,47 @@
       </c>
       <c r="B57">
         <f t="shared" ref="B57:L57" si="30">B16-B37</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C57">
         <f t="shared" si="30"/>
-        <v>56.09</v>
+        <v>-2.8200000000000074</v>
       </c>
       <c r="D57">
         <f t="shared" si="30"/>
-        <v>10.519999999999996</v>
+        <v>-2.4500000000000028</v>
       </c>
       <c r="E57">
         <f t="shared" si="30"/>
-        <v>-32.47</v>
+        <v>-2.2600000000000051</v>
       </c>
       <c r="F57">
         <f t="shared" si="30"/>
-        <v>-73.42</v>
+        <v>-1.9500000000000028</v>
       </c>
       <c r="G57">
         <f t="shared" si="30"/>
-        <v>-112.43</v>
+        <v>-2.7000000000000028</v>
       </c>
       <c r="H57">
         <f t="shared" si="30"/>
-        <v>-149.51</v>
+        <v>-3.5799999999999983</v>
       </c>
       <c r="I57">
         <f t="shared" si="30"/>
-        <v>-182.57</v>
+        <v>-4.5600000000000023</v>
       </c>
       <c r="J57">
         <f t="shared" si="30"/>
-        <v>-211.61</v>
+        <v>-5.6399999999999988</v>
       </c>
       <c r="K57">
         <f t="shared" si="30"/>
-        <v>-239.06</v>
+        <v>-6.72</v>
       </c>
       <c r="L57">
         <f t="shared" si="30"/>
-        <v>-262.81</v>
+        <v>-7.5200000000000005</v>
       </c>
       <c r="O57">
         <f t="shared" ref="O57:Y57" si="31">O16-O37</f>
@@ -7619,47 +7619,47 @@
       </c>
       <c r="B58">
         <f t="shared" ref="B58:L58" si="32">B17-B38</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C58">
         <f t="shared" si="32"/>
-        <v>55.47999999999999</v>
+        <v>-2.0300000000000011</v>
       </c>
       <c r="D58">
         <f t="shared" si="32"/>
-        <v>8.0499999999999972</v>
+        <v>-1.8500000000000085</v>
       </c>
       <c r="E58">
         <f t="shared" si="32"/>
-        <v>-36.24</v>
+        <v>-1.6500000000000057</v>
       </c>
       <c r="F58">
         <f t="shared" si="32"/>
-        <v>-78.989999999999995</v>
+        <v>-1.2800000000000011</v>
       </c>
       <c r="G58">
         <f t="shared" si="32"/>
-        <v>-120.45</v>
+        <v>-1.5699999999999932</v>
       </c>
       <c r="H58">
         <f t="shared" si="32"/>
-        <v>-159.11000000000001</v>
+        <v>-2.259999999999998</v>
       </c>
       <c r="I58">
         <f t="shared" si="32"/>
-        <v>-191.78</v>
+        <v>-2.740000000000002</v>
       </c>
       <c r="J58">
         <f t="shared" si="32"/>
-        <v>-221.76</v>
+        <v>-3.9699999999999989</v>
       </c>
       <c r="K58">
         <f t="shared" si="32"/>
-        <v>-250.82</v>
+        <v>-5.3999999999999995</v>
       </c>
       <c r="L58">
         <f t="shared" si="32"/>
-        <v>-278.06</v>
+        <v>-6.43</v>
       </c>
       <c r="O58">
         <f t="shared" ref="O58:Y58" si="33">O17-O38</f>
@@ -7712,47 +7712,47 @@
       </c>
       <c r="B59">
         <f t="shared" ref="B59:L59" si="34">B18-B39</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C59">
         <f t="shared" si="34"/>
-        <v>54.430000000000007</v>
+        <v>-2.0900000000000034</v>
       </c>
       <c r="D59">
         <f t="shared" si="34"/>
-        <v>6.2399999999999949</v>
+        <v>-1.5200000000000102</v>
       </c>
       <c r="E59">
         <f t="shared" si="34"/>
-        <v>-39.390000000000008</v>
+        <v>-1.6200000000000045</v>
       </c>
       <c r="F59">
         <f t="shared" si="34"/>
-        <v>-83.53</v>
+        <v>-1.3500000000000085</v>
       </c>
       <c r="G59">
         <f t="shared" si="34"/>
-        <v>-125.80000000000001</v>
+        <v>-0.51000000000000512</v>
       </c>
       <c r="H59">
         <f t="shared" si="34"/>
-        <v>-166.31</v>
+        <v>-1.0900000000000034</v>
       </c>
       <c r="I59">
         <f t="shared" si="34"/>
-        <v>-199.95999999999998</v>
+        <v>-1.8300000000000018</v>
       </c>
       <c r="J59">
         <f t="shared" si="34"/>
-        <v>-230.34</v>
+        <v>-2.4800000000000004</v>
       </c>
       <c r="K59">
         <f t="shared" si="34"/>
-        <v>-260.42</v>
+        <v>-3.96</v>
       </c>
       <c r="L59">
         <f t="shared" si="34"/>
-        <v>-289.74</v>
+        <v>-5.2399999999999984</v>
       </c>
       <c r="O59">
         <f t="shared" ref="O59:Y59" si="35">O18-O39</f>
@@ -7805,47 +7805,47 @@
       </c>
       <c r="B60">
         <f t="shared" ref="B60:L60" si="36">B19-B40</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C60">
         <f t="shared" si="36"/>
-        <v>54.36</v>
+        <v>-1.5799999999999983</v>
       </c>
       <c r="D60">
         <f t="shared" si="36"/>
-        <v>5.5999999999999943</v>
+        <v>-0.93000000000000682</v>
       </c>
       <c r="E60">
         <f t="shared" si="36"/>
-        <v>-40.540000000000006</v>
+        <v>-0.81000000000000227</v>
       </c>
       <c r="F60">
         <f t="shared" si="36"/>
-        <v>-85.429999999999993</v>
+        <v>-0.38999999999998636</v>
       </c>
       <c r="G60">
         <f t="shared" si="36"/>
-        <v>-129.24</v>
+        <v>-0.21999999999999886</v>
       </c>
       <c r="H60">
         <f t="shared" si="36"/>
-        <v>-170.51</v>
+        <v>-0.60999999999999943</v>
       </c>
       <c r="I60">
         <f t="shared" si="36"/>
-        <v>-205.53</v>
+        <v>-1.129999999999999</v>
       </c>
       <c r="J60">
         <f t="shared" si="36"/>
-        <v>-237.23999999999998</v>
+        <v>-1.7599999999999998</v>
       </c>
       <c r="K60">
         <f t="shared" si="36"/>
-        <v>-267.84999999999997</v>
+        <v>-2.74</v>
       </c>
       <c r="L60">
         <f t="shared" si="36"/>
-        <v>-298.28999999999996</v>
+        <v>-4.18</v>
       </c>
       <c r="O60">
         <f t="shared" ref="O60:Y60" si="37">O19-O40</f>
@@ -7898,47 +7898,47 @@
       </c>
       <c r="B61">
         <f t="shared" ref="B61:L61" si="38">B20-B41</f>
-        <v>107.76999999999998</v>
+        <v>-0.81999999999999318</v>
       </c>
       <c r="C61">
         <f t="shared" si="38"/>
-        <v>54.830000000000013</v>
+        <v>-0.92000000000000171</v>
       </c>
       <c r="D61">
         <f t="shared" si="38"/>
-        <v>5.6900000000000119</v>
+        <v>-0.42999999999999261</v>
       </c>
       <c r="E61">
         <f t="shared" si="38"/>
-        <v>-40.729999999999997</v>
+        <v>-0.29999999999999716</v>
       </c>
       <c r="F61">
         <f t="shared" si="38"/>
-        <v>-86.23</v>
+        <v>-0.10999999999999943</v>
       </c>
       <c r="G61">
         <f t="shared" si="38"/>
-        <v>-129.91</v>
+        <v>0.38000000000000256</v>
       </c>
       <c r="H61">
         <f t="shared" si="38"/>
-        <v>-170.99</v>
+        <v>0.26999999999999602</v>
       </c>
       <c r="I61">
         <f t="shared" si="38"/>
-        <v>-206.53</v>
+        <v>-0.37000000000000099</v>
       </c>
       <c r="J61">
         <f t="shared" si="38"/>
-        <v>-239.73000000000002</v>
+        <v>-1.1999999999999997</v>
       </c>
       <c r="K61">
         <f t="shared" si="38"/>
-        <v>-271.45</v>
+        <v>-2.129999999999999</v>
       </c>
       <c r="L61">
         <f t="shared" si="38"/>
-        <v>-302.06</v>
+        <v>-3.6500000000000021</v>
       </c>
       <c r="O61">
         <f t="shared" ref="O61:Y61" si="39">O20-O41</f>
@@ -7988,6 +7988,7 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>